--- a/submission/COMAVI_v7.15_SI/S3_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S3_Table.xlsx
@@ -638,7 +638,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -692,45 +691,29 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.920</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.579</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.720</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.545</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.710</t>
-        </is>
+      <c r="B4" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.667</v>
       </c>
     </row>
     <row r="5">
@@ -739,45 +722,29 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.680</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.594</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.649</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.680</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.727</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.734</t>
-        </is>
+      <c r="B5" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -786,45 +753,29 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.640</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.684</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.727</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.767</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.742</t>
-        </is>
+      <c r="B6" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.699</v>
       </c>
     </row>
     <row r="7">
@@ -833,45 +784,29 @@
           <t>2.5 (reference)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.560</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.812</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.773</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.733</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.742</t>
-        </is>
+      <c r="B7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.699</v>
       </c>
     </row>
     <row r="8">
@@ -880,45 +815,29 @@
           <t>2.9/2.9/3.5</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.720</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.480</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.844</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.711</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.720</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.727</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.733</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.726</t>
-        </is>
+      <c r="B8" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -927,45 +846,31 @@
           <t>3.0 (post hoc)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.640</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.844</t>
-        </is>
+      <c r="B9" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.852</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.680</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.682</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.700</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.702</t>
-        </is>
+      <c r="F9" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.658</v>
       </c>
     </row>
     <row r="10">
@@ -974,45 +879,31 @@
           <t>3.5 (post hoc)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.520</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.360</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.844</t>
-        </is>
+      <c r="B10" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.852</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.640</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.682</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.733</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.702</t>
-        </is>
+      <c r="F10" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.658</v>
       </c>
     </row>
     <row r="11">
@@ -1021,45 +912,31 @@
           <t>4.0 (post hoc)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0.480</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.280</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.938</t>
-        </is>
+      <c r="B11" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.926</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.727</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.700</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.694</t>
-        </is>
+      <c r="F11" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +968,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1100,17 +976,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Structural arm (n = 25)</t>
+          <t>Structural arm (n = 29)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No-lesion arm (n = 32)</t>
+          <t>No-lesion arm (n = 27)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pooled score (n = 57)</t>
+          <t>Pooled score (n = 56)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1130,25 +1006,17 @@
           <t>1.0 default</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.438</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.579</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.599</t>
-        </is>
+      <c r="B4" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.5580000000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1162,25 +1030,17 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.720</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.594</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.649</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.657</t>
-        </is>
+      <c r="B5" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.615</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1194,25 +1054,17 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.640</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.684</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.679</t>
-        </is>
+      <c r="B6" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.655</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,25 +1078,17 @@
           <t>2.5 reference</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.812</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.706</t>
-        </is>
+      <c r="B7" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.666</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,25 +1102,17 @@
           <t>Prediction-interval bound</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.540</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.844</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.711</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.692</t>
-        </is>
+      <c r="B8" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.659</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1312,7 +1148,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1476,7 +1311,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1593,7 +1427,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1782,7 +1615,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1911,7 +1743,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2023,7 +1854,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2047,15 +1877,11 @@
           <t>Observed at 2.5</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.742</t>
-        </is>
+      <c r="B4" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.699</v>
       </c>
     </row>
     <row r="5">
@@ -2066,12 +1892,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.484 ± 0.052; p = 5 × 10^-4</t>
+          <t>0.464 ± 0.051; p = 5 × 10^-4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.535 ± 0.046; p = 5 × 10^-4</t>
+          <t>0.534 ± 0.046; p = 5 × 10^-4</t>
         </is>
       </c>
     </row>
@@ -2083,12 +1909,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.7037-0.7500</t>
+          <t>0.6415-0.6792</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7265-0.7589</t>
+          <t>0.6810-0.7238</t>
         </is>
       </c>
     </row>
@@ -2100,12 +1926,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.721 ± 0.013</t>
+          <t>0.661 ± 0.014</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.740 ± 0.004</t>
+          <t>0.697 ± 0.004</t>
         </is>
       </c>
     </row>
@@ -2117,12 +1943,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>95% CI 0.614-0.819</t>
+          <t>95% CI 0.546-0.769</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>95% CI 0.664-0.820</t>
+          <t>95% CI 0.609-0.779</t>
         </is>
       </c>
     </row>
@@ -2134,12 +1960,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>95% CI 0.625-0.821</t>
+          <t>95% CI 0.573-0.755</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>95% CI 0.682-0.816</t>
+          <t>95% CI 0.622-0.778</t>
         </is>
       </c>
     </row>
@@ -2172,7 +1998,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>

--- a/submission/COMAVI_v7.15_SI/S3_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S3_Table.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S3 Table, operating_point_sweep sheet. Complete operating-point sweep. The pooled score is the mechanism-pattern score over all 57 graded variants; the balanced score weights the structural and no-lesion arms equally. A measured destabilization (measured ΔΔG of at least 1.0 kcal/mol, n = 42) is recovered when the prediction reaches the threshold with the same sign.</t>
+          <t>S3 Table, operating_point_sweep sheet. Complete operating-point sweep. The pooled score is the mechanism-pattern score over all 56 graded variants; the balanced score weights the structural and no-lesion arms equally. A measured destabilization (measured ΔΔG of at least 1.0 kcal/mol, n = 42) is recovered when the prediction reaches the threshold with the same sign.</t>
         </is>
       </c>
     </row>
@@ -638,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -964,10 +965,11 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>S3 Table, operating_point_sweep sheet. Complete operating-point sweep. The pooled score is the mechanism-pattern score over all 57 graded variants; the balanced score weights the structural and no-lesion arms equally. A measured destabilization (measured ΔΔG of at least 1.0 kcal/mol, n = 42) is recovered when the prediction reaches the threshold with the same sign.</t>
-        </is>
-      </c>
-    </row>
+          <t>S3 Table, operating_point_sweep sheet. Complete operating-point sweep. The pooled score is the mechanism-pattern score over all 56 graded variants; the balanced score weights the structural and no-lesion arms equally. A measured destabilization (measured ΔΔG of at least 1.0 kcal/mol, n = 42) is recovered when the prediction reaches the threshold with the same sign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1148,6 +1150,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1311,6 +1314,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1427,6 +1431,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1615,6 +1620,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1743,6 +1749,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1854,6 +1861,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1998,6 +2006,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>

--- a/submission/COMAVI_v7.15_SI/S3_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S3_Table.xlsx
@@ -638,7 +638,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -969,7 +968,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1150,7 +1148,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1372,12 +1369,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6/17 = 0.353</t>
+          <t>6/16 = 0.375</t>
         </is>
       </c>
     </row>
@@ -1389,17 +1386,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0/17 = 0.000</t>
+          <t>4/17 = 0.235</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1428,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1620,7 +1616,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1749,7 +1744,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1861,7 +1855,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2006,7 +1999,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>

--- a/submission/COMAVI_v7.15_SI/S3_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S3_Table.xlsx
@@ -638,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -788,7 +789,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.483</v>
+        <v>0.517</v>
       </c>
       <c r="D7" t="n">
         <v>0.8149999999999999</v>
@@ -819,7 +820,7 @@
         <v>0.621</v>
       </c>
       <c r="C8" t="n">
-        <v>0.414</v>
+        <v>0.448</v>
       </c>
       <c r="D8" t="n">
         <v>0.852</v>
@@ -850,7 +851,7 @@
         <v>0.552</v>
       </c>
       <c r="C9" t="n">
-        <v>0.345</v>
+        <v>0.379</v>
       </c>
       <c r="D9" t="n">
         <v>0.852</v>
@@ -883,7 +884,7 @@
         <v>0.448</v>
       </c>
       <c r="C10" t="n">
-        <v>0.31</v>
+        <v>0.345</v>
       </c>
       <c r="D10" t="n">
         <v>0.852</v>
@@ -916,7 +917,7 @@
         <v>0.414</v>
       </c>
       <c r="C11" t="n">
-        <v>0.241</v>
+        <v>0.276</v>
       </c>
       <c r="D11" t="n">
         <v>0.926</v>
@@ -1311,7 +1312,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>

--- a/submission/COMAVI_v7.15_SI/S3_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S3_Table.xlsx
@@ -969,6 +969,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1100,7 +1101,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prediction-interval bound</t>
+          <t>Prediction-interval limit</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1149,6 +1150,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1312,6 +1314,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1428,6 +1431,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1566,7 +1570,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prediction-interval bound</t>
+          <t>Prediction-interval limit</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1616,6 +1620,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1704,7 +1709,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prediction-interval bound</t>
+          <t>Prediction-interval limit</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1744,6 +1749,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1855,6 +1861,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1999,6 +2006,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
